--- a/r-data/top10_other_abundance.xlsx
+++ b/r-data/top10_other_abundance.xlsx
@@ -423,37 +423,37 @@
         </is>
       </c>
       <c r="B2">
-        <v>10.14309097629231</v>
+        <v>10.1430909762923</v>
       </c>
       <c r="C2">
-        <v>0.05412112571941496</v>
+        <v>0.05412112571941494</v>
       </c>
       <c r="D2">
         <v>57.02518612387137</v>
       </c>
       <c r="E2">
-        <v>0.01848038439199536</v>
+        <v>0.01848038439199534</v>
       </c>
       <c r="F2">
-        <v>0.07392153756798142</v>
+        <v>0.07392153756798144</v>
       </c>
       <c r="G2">
-        <v>0.003960082369713291</v>
+        <v>0.003960082369713289</v>
       </c>
       <c r="H2">
-        <v>0.2983262051850679</v>
+        <v>0.2983262051850677</v>
       </c>
       <c r="I2">
-        <v>1.364908390094514</v>
+        <v>1.364908390094513</v>
       </c>
       <c r="J2">
         <v>29.47357305031944</v>
       </c>
       <c r="K2">
-        <v>1.508791382860764</v>
+        <v>1.508791382860763</v>
       </c>
       <c r="L2">
-        <v>0.03564074132741961</v>
+        <v>0.03564074132741959</v>
       </c>
     </row>
     <row r="3">
@@ -466,34 +466,34 @@
         <v>22.17382121548128</v>
       </c>
       <c r="C3">
-        <v>0.009240192195997678</v>
+        <v>0.009240192195997672</v>
       </c>
       <c r="D3">
-        <v>28.41227097523629</v>
+        <v>28.41227097523628</v>
       </c>
       <c r="E3">
-        <v>0.007920164739426581</v>
+        <v>0.007920164739426576</v>
       </c>
       <c r="F3">
-        <v>0.06072126300227045</v>
+        <v>0.06072126300227046</v>
       </c>
       <c r="G3">
-        <v>0.006600137282855484</v>
+        <v>0.006600137282855481</v>
       </c>
       <c r="H3">
-        <v>2.307407994086277</v>
+        <v>2.307407994086276</v>
       </c>
       <c r="I3">
-        <v>1.623633771582449</v>
+        <v>1.623633771582448</v>
       </c>
       <c r="J3">
-        <v>43.82359153070384</v>
+        <v>43.82359153070382</v>
       </c>
       <c r="K3">
-        <v>1.557632398753894</v>
+        <v>1.557632398753893</v>
       </c>
       <c r="L3">
-        <v>0.01716035693542426</v>
+        <v>0.01716035693542425</v>
       </c>
     </row>
     <row r="4">
@@ -503,37 +503,37 @@
         </is>
       </c>
       <c r="B4">
-        <v>8.161729763979091</v>
+        <v>8.161729763979089</v>
       </c>
       <c r="C4">
-        <v>0.355087385817625</v>
+        <v>0.3550873858176248</v>
       </c>
       <c r="D4">
-        <v>33.77290247637151</v>
+        <v>33.77290247637153</v>
       </c>
       <c r="E4">
-        <v>0.05280109826284387</v>
+        <v>0.05280109826284386</v>
       </c>
       <c r="F4">
-        <v>0.1082422514388299</v>
+        <v>0.10824225143883</v>
       </c>
       <c r="G4">
         <v>0.03168065895770632</v>
       </c>
       <c r="H4">
-        <v>0.4857701040181636</v>
+        <v>0.4857701040181635</v>
       </c>
       <c r="I4">
-        <v>0.9821004276888959</v>
+        <v>0.9821004276888954</v>
       </c>
       <c r="J4">
-        <v>54.58577538412798</v>
+        <v>54.585775384128</v>
       </c>
       <c r="K4">
-        <v>0.6230529595015577</v>
+        <v>0.6230529595015575</v>
       </c>
       <c r="L4">
-        <v>0.8408574898357885</v>
+        <v>0.8408574898357883</v>
       </c>
     </row>
     <row r="5">
@@ -549,19 +549,19 @@
         <v>0.01056021965256877</v>
       </c>
       <c r="D5">
-        <v>1.836158192090396</v>
+        <v>1.836158192090395</v>
       </c>
       <c r="E5">
-        <v>0.001320027456571097</v>
+        <v>0.001320027456571096</v>
       </c>
       <c r="F5">
-        <v>0.2692856011405037</v>
+        <v>0.2692856011405034</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>0.1663234595279582</v>
+        <v>0.1663234595279581</v>
       </c>
       <c r="I5">
         <v>0.2244046676170864</v>
@@ -573,7 +573,7 @@
         <v>0.03300068641427741</v>
       </c>
       <c r="L5">
-        <v>0.006600137282855484</v>
+        <v>0.006600137282855482</v>
       </c>
     </row>
     <row r="6">
@@ -583,25 +583,25 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.8104968583346533</v>
+        <v>0.8104968583346528</v>
       </c>
       <c r="C6">
-        <v>0.002640054913142194</v>
+        <v>0.002640054913142193</v>
       </c>
       <c r="D6">
-        <v>2.374729394371403</v>
+        <v>2.374729394371404</v>
       </c>
       <c r="E6">
-        <v>0.005280109826284387</v>
+        <v>0.005280109826284385</v>
       </c>
       <c r="F6">
         <v>0.06336131791541265</v>
       </c>
       <c r="G6">
-        <v>0.002640054913142194</v>
+        <v>0.002640054913142193</v>
       </c>
       <c r="H6">
-        <v>0.7484555678758119</v>
+        <v>0.7484555678758116</v>
       </c>
       <c r="I6">
         <v>0.1465230476793917</v>
@@ -613,7 +613,7 @@
         <v>0.01452030202228206</v>
       </c>
       <c r="L6">
-        <v>0.08448175722055019</v>
+        <v>0.08448175722055017</v>
       </c>
     </row>
     <row r="7">
@@ -623,13 +623,13 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.9187391097734832</v>
+        <v>0.9187391097734827</v>
       </c>
       <c r="C7">
         <v>2.87633982786842</v>
       </c>
       <c r="D7">
-        <v>79.02080363271557</v>
+        <v>79.02080363271556</v>
       </c>
       <c r="E7">
         <v>14.10845345583188</v>
@@ -638,19 +638,19 @@
         <v>0.1003220866994034</v>
       </c>
       <c r="G7">
-        <v>0.002640054913142194</v>
+        <v>0.002640054913142192</v>
       </c>
       <c r="H7">
         <v>0</v>
       </c>
       <c r="I7">
-        <v>2.382649559110829</v>
+        <v>2.382649559110827</v>
       </c>
       <c r="J7">
-        <v>0.2666455462273615</v>
+        <v>0.2666455462273614</v>
       </c>
       <c r="K7">
-        <v>0.2930460953587835</v>
+        <v>0.2930460953587833</v>
       </c>
       <c r="L7">
         <v>0.03036063150113522</v>
@@ -663,37 +663,37 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.2890860129890702</v>
+        <v>0.2890860129890699</v>
       </c>
       <c r="C8">
-        <v>5.097946037277575</v>
+        <v>5.097946037277574</v>
       </c>
       <c r="D8">
         <v>12.73958498336765</v>
       </c>
       <c r="E8">
-        <v>6.670098738053752</v>
+        <v>6.670098738053751</v>
       </c>
       <c r="F8">
         <v>11.33507576957601</v>
       </c>
       <c r="G8">
-        <v>5.829241248217962</v>
+        <v>5.829241248217961</v>
       </c>
       <c r="H8">
         <v>0.1716035693542425</v>
       </c>
       <c r="I8">
-        <v>0.7418554305929563</v>
+        <v>0.7418554305929559</v>
       </c>
       <c r="J8">
         <v>11.88552721896615</v>
       </c>
       <c r="K8">
-        <v>0.002640054913142194</v>
+        <v>0.002640054913142192</v>
       </c>
       <c r="L8">
-        <v>45.23734093669148</v>
+        <v>45.2373409366915</v>
       </c>
     </row>
     <row r="9">
@@ -721,7 +721,7 @@
         <v>0.02640054913142193</v>
       </c>
       <c r="H9">
-        <v>9.405195628069064</v>
+        <v>9.405195628069063</v>
       </c>
       <c r="I9">
         <v>2.6123343365542</v>
@@ -733,7 +733,7 @@
         <v>1.198584930566556</v>
       </c>
       <c r="L9">
-        <v>0.07656159248112361</v>
+        <v>0.0765615924811236</v>
       </c>
     </row>
   </sheetData>
